--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.08800094160302</v>
+        <v>3.91430015301049</v>
       </c>
       <c r="D2" t="n">
-        <v>24.43671810458746</v>
+        <v>3.970966691995463</v>
       </c>
       <c r="E2" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F2" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5865719661061</v>
+        <v>2.857817944492241</v>
       </c>
       <c r="D3" t="n">
-        <v>32.10140183854904</v>
+        <v>5.21647779876422</v>
       </c>
       <c r="E3" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F3" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.375071422065236</v>
+        <v>1.360949106085601</v>
       </c>
       <c r="D4" t="n">
-        <v>9.974817476389644</v>
+        <v>1.620907839913317</v>
       </c>
       <c r="E4" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F4" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.186903731090196</v>
+        <v>1.005371856302157</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F5" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.4986522415117</v>
+        <v>4.956030989245652</v>
       </c>
       <c r="D6" t="n">
-        <v>31.8473901968584</v>
+        <v>5.17520090698949</v>
       </c>
       <c r="E6" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F6" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.36020167210506</v>
+        <v>2.658532771717072</v>
       </c>
       <c r="D7" t="n">
-        <v>16.18206083239568</v>
+        <v>2.629584885264298</v>
       </c>
       <c r="E7" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F7" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.522601868107833</v>
+        <v>1.384922803567523</v>
       </c>
       <c r="D8" t="n">
-        <v>9.947082207584518</v>
+        <v>1.616400858732484</v>
       </c>
       <c r="E8" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F8" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>2.87011436271953</v>
+        <v>0.4663935839419237</v>
       </c>
       <c r="D9" t="n">
-        <v>16.28868691759381</v>
+        <v>2.646911624108995</v>
       </c>
       <c r="E9" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F9" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.43882483110992</v>
+        <v>5.108809035055363</v>
       </c>
       <c r="D10" t="n">
-        <v>27.49293054185408</v>
+        <v>4.467601213051288</v>
       </c>
       <c r="E10" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F10" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.35750659714613</v>
+        <v>2.333094822036246</v>
       </c>
       <c r="D11" t="n">
-        <v>17.33098374628619</v>
+        <v>2.816284858771505</v>
       </c>
       <c r="E11" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F11" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.98790161663112</v>
+        <v>3.573034012702557</v>
       </c>
       <c r="D12" t="n">
-        <v>16.91542590994623</v>
+        <v>2.748756710366263</v>
       </c>
       <c r="E12" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F12" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.27403918168109</v>
+        <v>3.619531367023177</v>
       </c>
       <c r="D13" t="n">
-        <v>22.70226906650343</v>
+        <v>3.689118723306807</v>
       </c>
       <c r="E13" t="n">
-        <v>8.963683099663658</v>
+        <v>1.456598503695345</v>
       </c>
       <c r="F13" t="n">
-        <v>8.195858355961587</v>
+        <v>1.331826982843758</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
